--- a/reports/paper_trading_performance.xlsx
+++ b/reports/paper_trading_performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="26">
   <si>
     <t>timestamp</t>
   </si>
@@ -460,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1225,6 +1225,120 @@
       </c>
       <c r="L20">
         <v>12.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="3">
+        <v>46186.16352501582</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21">
+        <v>0.072474</v>
+      </c>
+      <c r="E21">
+        <v>7434.58</v>
+      </c>
+      <c r="F21">
+        <v>538.8099999999999</v>
+      </c>
+      <c r="G21">
+        <v>0.27</v>
+      </c>
+      <c r="H21">
+        <v>9961.396561979996</v>
+      </c>
+      <c r="I21">
+        <v>15.29372664624316</v>
+      </c>
+      <c r="J21">
+        <v>-53.89716466624392</v>
+      </c>
+      <c r="K21">
+        <v>-38.60343802000077</v>
+      </c>
+      <c r="L21">
+        <v>12.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="3">
+        <v>46186.16824081628</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22">
+        <v>0.067011</v>
+      </c>
+      <c r="E22">
+        <v>7434.58</v>
+      </c>
+      <c r="F22">
+        <v>498.2</v>
+      </c>
+      <c r="G22">
+        <v>0.25</v>
+      </c>
+      <c r="H22">
+        <v>9961.395202359996</v>
+      </c>
+      <c r="I22">
+        <v>15.29236702624303</v>
+      </c>
+      <c r="J22">
+        <v>-53.89716466624392</v>
+      </c>
+      <c r="K22">
+        <v>-38.6047976400009</v>
+      </c>
+      <c r="L22">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="3">
+        <v>46186.17084117234</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23">
+        <v>0.002659</v>
+      </c>
+      <c r="E23">
+        <v>7427.14</v>
+      </c>
+      <c r="F23">
+        <v>19.75</v>
+      </c>
+      <c r="G23">
+        <v>0.01</v>
+      </c>
+      <c r="H23">
+        <v>9958.215524619996</v>
+      </c>
+      <c r="I23">
+        <v>12.03613011580455</v>
+      </c>
+      <c r="J23">
+        <v>-53.8206054958056</v>
+      </c>
+      <c r="K23">
+        <v>-41.78447538000105</v>
+      </c>
+      <c r="L23">
+        <v>13.2</v>
       </c>
     </row>
   </sheetData>
@@ -1254,7 +1368,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1262,7 +1376,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1270,7 +1384,7 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1278,7 +1392,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>12.67</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1286,7 +1400,7 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>25353.91</v>
+        <v>26410.67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1294,7 +1408,7 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>-53.9</v>
+        <v>-53.82</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1302,7 +1416,7 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>12.79</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1310,7 +1424,7 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>-41.11</v>
+        <v>-41.78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1318,7 +1432,7 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>9958.889999999999</v>
+        <v>9958.219999999999</v>
       </c>
     </row>
   </sheetData>

--- a/reports/paper_trading_performance.xlsx
+++ b/reports/paper_trading_performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="26">
   <si>
     <t>timestamp</t>
   </si>
@@ -460,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1339,6 +1339,44 @@
       </c>
       <c r="L23">
         <v>13.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="3">
+        <v>46186.18980320596</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <v>0.00536</v>
+      </c>
+      <c r="E24">
+        <v>7434.58</v>
+      </c>
+      <c r="F24">
+        <v>39.85</v>
+      </c>
+      <c r="G24">
+        <v>0.02</v>
+      </c>
+      <c r="H24">
+        <v>9961.376002939996</v>
+      </c>
+      <c r="I24">
+        <v>15.19660843580459</v>
+      </c>
+      <c r="J24">
+        <v>-53.8206054958056</v>
+      </c>
+      <c r="K24">
+        <v>-38.62399706000101</v>
+      </c>
+      <c r="L24">
+        <v>13.22</v>
       </c>
     </row>
   </sheetData>
@@ -1368,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1376,7 +1414,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1392,7 +1430,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>13.2</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1400,7 +1438,7 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>26410.67</v>
+        <v>26450.52</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1416,7 +1454,7 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>12.04</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1424,7 +1462,7 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>-41.78</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1432,7 +1470,7 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>9958.219999999999</v>
+        <v>9961.379999999999</v>
       </c>
     </row>
   </sheetData>

--- a/reports/paper_trading_performance.xlsx
+++ b/reports/paper_trading_performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
   <si>
     <t>timestamp</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>SPX</t>
+  </si>
+  <si>
+    <t>Gold</t>
   </si>
   <si>
     <t>Metric</t>
@@ -460,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1377,6 +1380,82 @@
       </c>
       <c r="L24">
         <v>13.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="3">
+        <v>46186.19893202635</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>0.251223</v>
+      </c>
+      <c r="E25">
+        <v>4242.02</v>
+      </c>
+      <c r="F25">
+        <v>1065.69</v>
+      </c>
+      <c r="G25">
+        <v>0.53</v>
+      </c>
+      <c r="H25">
+        <v>9961.378993399996</v>
+      </c>
+      <c r="I25">
+        <v>15.19959889580446</v>
+      </c>
+      <c r="J25">
+        <v>-53.8206054958056</v>
+      </c>
+      <c r="K25">
+        <v>-38.62100660000115</v>
+      </c>
+      <c r="L25">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="3">
+        <v>46186.20421433327</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>0.083158</v>
+      </c>
+      <c r="E26">
+        <v>7427.14</v>
+      </c>
+      <c r="F26">
+        <v>617.63</v>
+      </c>
+      <c r="G26">
+        <v>0.31</v>
+      </c>
+      <c r="H26">
+        <v>9958.181877359995</v>
+      </c>
+      <c r="I26">
+        <v>9.680063660558744</v>
+      </c>
+      <c r="J26">
+        <v>-51.49818630055986</v>
+      </c>
+      <c r="K26">
+        <v>-41.81812264000111</v>
+      </c>
+      <c r="L26">
+        <v>14.06</v>
       </c>
     </row>
   </sheetData>
@@ -1395,82 +1474,82 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>13.22</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>26450.52</v>
+        <v>28133.84</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>-53.82</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>15.2</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>-38.62</v>
+        <v>-41.82</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>9961.379999999999</v>
+        <v>9958.18</v>
       </c>
     </row>
   </sheetData>

--- a/reports/paper_trading_performance.xlsx
+++ b/reports/paper_trading_performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="27">
   <si>
     <t>timestamp</t>
   </si>
@@ -463,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1456,6 +1456,82 @@
       </c>
       <c r="L26">
         <v>14.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3">
+        <v>46186.5862034704</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>0.109921</v>
+      </c>
+      <c r="E27">
+        <v>7427.14</v>
+      </c>
+      <c r="F27">
+        <v>816.4</v>
+      </c>
+      <c r="G27">
+        <v>0.41</v>
+      </c>
+      <c r="H27">
+        <v>9958.183221419997</v>
+      </c>
+      <c r="I27">
+        <v>6.615357426412629</v>
+      </c>
+      <c r="J27">
+        <v>-48.43213600641379</v>
+      </c>
+      <c r="K27">
+        <v>-41.81677858000116</v>
+      </c>
+      <c r="L27">
+        <v>14.47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3">
+        <v>46186.58621225939</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>0.084497</v>
+      </c>
+      <c r="E28">
+        <v>4237.78</v>
+      </c>
+      <c r="F28">
+        <v>358.08</v>
+      </c>
+      <c r="G28">
+        <v>0.18</v>
+      </c>
+      <c r="H28">
+        <v>9957.118339239996</v>
+      </c>
+      <c r="I28">
+        <v>5.907433367285421</v>
+      </c>
+      <c r="J28">
+        <v>-48.78909412728657</v>
+      </c>
+      <c r="K28">
+        <v>-42.88166076000115</v>
+      </c>
+      <c r="L28">
+        <v>14.65</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +1561,7 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1501,7 +1577,7 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1509,7 +1585,7 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>14.06</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1517,7 +1593,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>28133.84</v>
+        <v>29308.32</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1525,7 +1601,7 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>-51.5</v>
+        <v>-48.79</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1533,7 +1609,7 @@
         <v>24</v>
       </c>
       <c r="B8">
-        <v>9.68</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1541,7 +1617,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>-41.82</v>
+        <v>-42.88</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1549,7 +1625,7 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>9958.18</v>
+        <v>9957.120000000001</v>
       </c>
     </row>
   </sheetData>

--- a/reports/paper_trading_performance.xlsx
+++ b/reports/paper_trading_performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
   <si>
     <t>timestamp</t>
   </si>
@@ -59,10 +59,22 @@
     <t>SELL</t>
   </si>
   <si>
+    <t>Gold</t>
+  </si>
+  <si>
     <t>SPX</t>
   </si>
   <si>
-    <t>Gold</t>
+    <t>BTC</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>SPCE</t>
   </si>
   <si>
     <t>Metric</t>
@@ -463,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -510,7 +522,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="3">
-        <v>46182.64139989373</v>
+        <v>46188.95875970936</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -519,1019 +531,449 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>0.38599</v>
+        <v>0.530716</v>
       </c>
       <c r="E2">
-        <v>7409.51</v>
+        <v>4333.77</v>
       </c>
       <c r="F2">
-        <v>2860</v>
+        <v>2300</v>
       </c>
       <c r="G2">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="H2">
-        <v>9999.996764899999</v>
+        <v>10000.00107932</v>
       </c>
       <c r="I2">
-        <v>-0.003235099999983504</v>
+        <v>0.001079319999917061</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-0.003235099999983504</v>
+        <v>0.001079319999917061</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="3">
-        <v>46182.64642547358</v>
+        <v>46192.74335400779</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3">
-        <v>0.01768</v>
+        <v>0.530716</v>
       </c>
       <c r="E3">
-        <v>7409.51</v>
+        <v>4170.81</v>
       </c>
       <c r="F3">
-        <v>131</v>
+        <v>2213.52</v>
       </c>
       <c r="G3">
-        <v>0.07000000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H3">
-        <v>9999.9969017</v>
+        <v>9913.52</v>
       </c>
       <c r="I3">
-        <v>-0.003098300000146992</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="K3">
-        <v>-0.003098300000146992</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="3">
-        <v>46182.65537393943</v>
+        <v>46192.74410485572</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>0.165984</v>
+        <v>0.348754</v>
       </c>
       <c r="E4">
-        <v>7409.51</v>
+        <v>7504.33</v>
       </c>
       <c r="F4">
-        <v>1229.86</v>
+        <v>2617.17</v>
       </c>
       <c r="G4">
-        <v>0.61</v>
+        <v>1.31</v>
       </c>
       <c r="H4">
-        <v>9999.99700954</v>
+        <v>9913.51510482</v>
       </c>
       <c r="I4">
-        <v>-0.002990459999637096</v>
+        <v>-0.004895179999948596</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="K4">
-        <v>-0.002990459999637096</v>
+        <v>-86.48489517999997</v>
       </c>
       <c r="L4">
-        <v>2.11</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3">
-        <v>46182.65831098241</v>
+        <v>46192.74410984806</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0.294401</v>
+        <v>0.010361</v>
       </c>
       <c r="E5">
-        <v>7402.11</v>
+        <v>63151.56</v>
       </c>
       <c r="F5">
-        <v>2179.18</v>
+        <v>654.29</v>
       </c>
       <c r="G5">
-        <v>1.09</v>
+        <v>0.33</v>
       </c>
       <c r="H5">
-        <v>9995.77298383</v>
+        <v>9913.53841798</v>
       </c>
       <c r="I5">
-        <v>-2.038317170256278</v>
+        <v>0.01841798000009476</v>
       </c>
       <c r="J5">
-        <v>-2.188698999743792</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="K5">
-        <v>-4.22701617000007</v>
+        <v>-86.46158201999992</v>
       </c>
       <c r="L5">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="3">
-        <v>46182.67210367868</v>
+        <v>46192.74411552266</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>0.202495</v>
+        <v>19.846286</v>
       </c>
       <c r="E6">
-        <v>7409.51</v>
+        <v>210.8</v>
       </c>
       <c r="F6">
-        <v>1500.39</v>
+        <v>4183.5</v>
       </c>
       <c r="G6">
-        <v>0.75</v>
+        <v>2.09</v>
       </c>
       <c r="H6">
-        <v>9997.808583479999</v>
+        <v>9913.63550678</v>
       </c>
       <c r="I6">
-        <v>-0.002717520256283024</v>
+        <v>0.1155067800002598</v>
       </c>
       <c r="J6">
-        <v>-2.188698999743792</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="K6">
-        <v>-2.191416520000075</v>
+        <v>-86.36449321999976</v>
       </c>
       <c r="L6">
-        <v>3.95</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="3">
-        <v>46183.00150226162</v>
+        <v>46192.74412387348</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>0.222608</v>
+        <v>1.311278</v>
       </c>
       <c r="E7">
-        <v>7275.06</v>
+        <v>400.69</v>
       </c>
       <c r="F7">
-        <v>1619.49</v>
+        <v>525.42</v>
       </c>
       <c r="G7">
-        <v>0.8100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H7">
-        <v>9933.578808399998</v>
+        <v>9913.6314886</v>
       </c>
       <c r="I7">
-        <v>-34.30502428418799</v>
+        <v>0.1114886000002571</v>
       </c>
       <c r="J7">
-        <v>-32.11616731581216</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="K7">
-        <v>-66.42119160000016</v>
+        <v>-86.36851139999976</v>
       </c>
       <c r="L7">
-        <v>4.76</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="3">
-        <v>46183.16941442824</v>
+        <v>46192.74412879728</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>0.076603</v>
+        <v>542.744388</v>
       </c>
       <c r="E8">
-        <v>7390</v>
+        <v>3.56</v>
       </c>
       <c r="F8">
-        <v>566.09</v>
+        <v>1933.14</v>
       </c>
       <c r="G8">
-        <v>0.28</v>
+        <v>0.97</v>
       </c>
       <c r="H8">
-        <v>9962.910769999999</v>
+        <v>9912.661509879999</v>
       </c>
       <c r="I8">
-        <v>-4.973062684188335</v>
+        <v>-0.8584901199999422</v>
       </c>
       <c r="J8">
-        <v>-32.11616731581216</v>
+        <v>-86.48000000000002</v>
       </c>
       <c r="K8">
-        <v>-37.0892300000005</v>
+        <v>-87.33849011999996</v>
       </c>
       <c r="L8">
-        <v>5.04</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="3">
-        <v>46183.67161403567</v>
+        <v>46192.75053845254</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>0.07012500000000001</v>
+        <v>0.348754</v>
       </c>
       <c r="E9">
-        <v>7390</v>
+        <v>7494.11</v>
       </c>
       <c r="F9">
-        <v>518.22</v>
+        <v>2613.6</v>
       </c>
       <c r="G9">
-        <v>0.26</v>
+        <v>1.31</v>
       </c>
       <c r="H9">
-        <v>9962.914519999998</v>
+        <v>9909.09640506</v>
       </c>
       <c r="I9">
-        <v>-4.969312684188026</v>
+        <v>-0.8535949399999936</v>
       </c>
       <c r="J9">
-        <v>-32.11616731581216</v>
+        <v>-90.05000000000018</v>
       </c>
       <c r="K9">
-        <v>-37.08548000000019</v>
+        <v>-90.90359494000018</v>
       </c>
       <c r="L9">
-        <v>5.3</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="3">
-        <v>46183.83898239338</v>
+        <v>46192.75054402916</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>0.122762</v>
+        <v>0.010361</v>
       </c>
       <c r="E10">
-        <v>7382.62</v>
+        <v>63112.05</v>
       </c>
       <c r="F10">
-        <v>906.3099999999999</v>
+        <v>653.88</v>
       </c>
       <c r="G10">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="H10">
-        <v>9959.953537719997</v>
+        <v>9908.6630919</v>
       </c>
       <c r="I10">
-        <v>-5.511097197816071</v>
+        <v>-0.8769081000000369</v>
       </c>
       <c r="J10">
-        <v>-34.53536508218394</v>
+        <v>-90.46000000000015</v>
       </c>
       <c r="K10">
-        <v>-40.04646228000001</v>
+        <v>-91.33690810000019</v>
       </c>
       <c r="L10">
-        <v>5.75</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="3">
-        <v>46184.00548420261</v>
+        <v>46192.750550711</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>0.030717</v>
+        <v>19.846286</v>
       </c>
       <c r="E11">
-        <v>7319.07</v>
+        <v>210.12</v>
       </c>
       <c r="F11">
-        <v>224.82</v>
+        <v>4170.2</v>
       </c>
       <c r="G11">
-        <v>0.11</v>
+        <v>2.09</v>
       </c>
       <c r="H11">
-        <v>9942.216224609998</v>
+        <v>9895.2660031</v>
       </c>
       <c r="I11">
-        <v>-23.24841030781636</v>
+        <v>-0.973996900000202</v>
       </c>
       <c r="J11">
-        <v>-34.53536508218394</v>
+        <v>-103.7600000000003</v>
       </c>
       <c r="K11">
-        <v>-57.7837753900003</v>
+        <v>-104.7339969000005</v>
       </c>
       <c r="L11">
-        <v>5.86</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="3">
-        <v>46184.16826958509</v>
+        <v>46192.7505603496</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>0.18016</v>
+        <v>1.311278</v>
       </c>
       <c r="E12">
-        <v>7264.02</v>
+        <v>400.23</v>
       </c>
       <c r="F12">
-        <v>1308.68</v>
+        <v>524.8099999999999</v>
       </c>
       <c r="G12">
-        <v>0.65</v>
+        <v>0.26</v>
       </c>
       <c r="H12">
-        <v>9925.154625259998</v>
+        <v>9894.66002128</v>
       </c>
       <c r="I12">
-        <v>-16.86756352956309</v>
+        <v>-0.9699787200001992</v>
       </c>
       <c r="J12">
-        <v>-57.97781121043704</v>
+        <v>-104.3700000000003</v>
       </c>
       <c r="K12">
-        <v>-74.84537474000012</v>
+        <v>-105.3399787200005</v>
       </c>
       <c r="L12">
-        <v>6.510000000000001</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="3">
-        <v>46184.66928445282</v>
+        <v>46192.75056584376</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>0.124262</v>
+        <v>542.744388</v>
       </c>
       <c r="E13">
-        <v>7264.02</v>
+        <v>3.56</v>
       </c>
       <c r="F13">
-        <v>902.64</v>
+        <v>1931.2</v>
       </c>
       <c r="G13">
-        <v>0.45</v>
+        <v>0.97</v>
       </c>
       <c r="H13">
-        <v>9925.152972019998</v>
+        <v>9893.690000000001</v>
       </c>
       <c r="I13">
-        <v>-0.7026037545264643</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>-74.1444242254737</v>
+        <v>-106.3100000000004</v>
       </c>
       <c r="K13">
-        <v>-74.84702798000016</v>
+        <v>-106.3100000000004</v>
       </c>
       <c r="L13">
-        <v>6.960000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="3">
-        <v>46184.83820383177</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14">
-        <v>0.1311</v>
-      </c>
-      <c r="E14">
-        <v>7271.28</v>
-      </c>
-      <c r="F14">
-        <v>953.27</v>
-      </c>
-      <c r="G14">
-        <v>0.48</v>
-      </c>
-      <c r="H14">
-        <v>9925.186991279998</v>
-      </c>
-      <c r="I14">
-        <v>-0.6685844945263852</v>
-      </c>
-      <c r="J14">
-        <v>-74.1444242254737</v>
-      </c>
-      <c r="K14">
-        <v>-74.81300872000008</v>
-      </c>
-      <c r="L14">
-        <v>7.440000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="3">
-        <v>46185.0047344371</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15">
-        <v>0.023296</v>
-      </c>
-      <c r="E15">
-        <v>7273.15</v>
-      </c>
-      <c r="F15">
-        <v>169.44</v>
-      </c>
-      <c r="G15">
-        <v>0.08</v>
-      </c>
-      <c r="H15">
-        <v>9925.446945749998</v>
-      </c>
-      <c r="I15">
-        <v>-0.3427868933891887</v>
-      </c>
-      <c r="J15">
-        <v>-74.21026735661096</v>
-      </c>
-      <c r="K15">
-        <v>-74.55305425000014</v>
-      </c>
-      <c r="L15">
-        <v>7.520000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="3">
-        <v>46185.17212989987</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>0.769662</v>
-      </c>
-      <c r="E16">
-        <v>7396.76</v>
-      </c>
-      <c r="F16">
-        <v>5693</v>
-      </c>
-      <c r="G16">
-        <v>2.85</v>
-      </c>
-      <c r="H16">
-        <v>9939.445310919997</v>
-      </c>
-      <c r="I16">
-        <v>13.65557827661087</v>
-      </c>
-      <c r="J16">
-        <v>-74.21026735661096</v>
-      </c>
-      <c r="K16">
-        <v>-60.55468908000009</v>
-      </c>
-      <c r="L16">
-        <v>10.37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="3">
-        <v>46185.50554665483</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17">
-        <v>0.012222</v>
-      </c>
-      <c r="E17">
-        <v>7396.76</v>
-      </c>
-      <c r="F17">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="G17">
-        <v>0.05</v>
-      </c>
-      <c r="H17">
-        <v>9939.448511639997</v>
-      </c>
-      <c r="I17">
-        <v>13.65877899661064</v>
-      </c>
-      <c r="J17">
-        <v>-74.21026735661096</v>
-      </c>
-      <c r="K17">
-        <v>-60.55148836000032</v>
-      </c>
-      <c r="L17">
-        <v>10.42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="3">
-        <v>46185.66852058665</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18">
-        <v>0.026891</v>
-      </c>
-      <c r="E18">
-        <v>7389.36</v>
-      </c>
-      <c r="F18">
-        <v>198.71</v>
-      </c>
-      <c r="G18">
-        <v>0.1</v>
-      </c>
-      <c r="H18">
-        <v>9932.827573279996</v>
-      </c>
-      <c r="I18">
-        <v>6.82376552286496</v>
-      </c>
-      <c r="J18">
-        <v>-73.99619224286627</v>
-      </c>
-      <c r="K18">
-        <v>-67.17242672000131</v>
-      </c>
-      <c r="L18">
-        <v>10.52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="3">
-        <v>46185.83506709221</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19">
-        <v>0.154629</v>
-      </c>
-      <c r="E19">
-        <v>7389.36</v>
-      </c>
-      <c r="F19">
-        <v>1142.61</v>
-      </c>
-      <c r="G19">
-        <v>0.57</v>
-      </c>
-      <c r="H19">
-        <v>9932.828225839996</v>
-      </c>
-      <c r="I19">
-        <v>5.608429805626656</v>
-      </c>
-      <c r="J19">
-        <v>-72.78020396562758</v>
-      </c>
-      <c r="K19">
-        <v>-67.17177416000092</v>
-      </c>
-      <c r="L19">
-        <v>11.09</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="3">
-        <v>46186.00035793288</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20">
-        <v>0.425512</v>
-      </c>
-      <c r="E20">
-        <v>7425.89</v>
-      </c>
-      <c r="F20">
-        <v>3159.8</v>
-      </c>
-      <c r="G20">
-        <v>1.58</v>
-      </c>
-      <c r="H20">
-        <v>9958.889595729997</v>
-      </c>
-      <c r="I20">
-        <v>12.78676039624315</v>
-      </c>
-      <c r="J20">
-        <v>-53.89716466624392</v>
-      </c>
-      <c r="K20">
-        <v>-41.11040427000077</v>
-      </c>
-      <c r="L20">
-        <v>12.67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="3">
-        <v>46186.16352501582</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21">
-        <v>0.072474</v>
-      </c>
-      <c r="E21">
-        <v>7434.58</v>
-      </c>
-      <c r="F21">
-        <v>538.8099999999999</v>
-      </c>
-      <c r="G21">
-        <v>0.27</v>
-      </c>
-      <c r="H21">
-        <v>9961.396561979996</v>
-      </c>
-      <c r="I21">
-        <v>15.29372664624316</v>
-      </c>
-      <c r="J21">
-        <v>-53.89716466624392</v>
-      </c>
-      <c r="K21">
-        <v>-38.60343802000077</v>
-      </c>
-      <c r="L21">
-        <v>12.94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="3">
-        <v>46186.16824081628</v>
-      </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22">
-        <v>0.067011</v>
-      </c>
-      <c r="E22">
-        <v>7434.58</v>
-      </c>
-      <c r="F22">
-        <v>498.2</v>
-      </c>
-      <c r="G22">
-        <v>0.25</v>
-      </c>
-      <c r="H22">
-        <v>9961.395202359996</v>
-      </c>
-      <c r="I22">
-        <v>15.29236702624303</v>
-      </c>
-      <c r="J22">
-        <v>-53.89716466624392</v>
-      </c>
-      <c r="K22">
-        <v>-38.6047976400009</v>
-      </c>
-      <c r="L22">
-        <v>13.19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="3">
-        <v>46186.17084117234</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23">
-        <v>0.002659</v>
-      </c>
-      <c r="E23">
-        <v>7427.14</v>
-      </c>
-      <c r="F23">
-        <v>19.75</v>
-      </c>
-      <c r="G23">
-        <v>0.01</v>
-      </c>
-      <c r="H23">
-        <v>9958.215524619996</v>
-      </c>
-      <c r="I23">
-        <v>12.03613011580455</v>
-      </c>
-      <c r="J23">
-        <v>-53.8206054958056</v>
-      </c>
-      <c r="K23">
-        <v>-41.78447538000105</v>
-      </c>
-      <c r="L23">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="3">
-        <v>46186.18980320596</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24">
-        <v>0.00536</v>
-      </c>
-      <c r="E24">
-        <v>7434.58</v>
-      </c>
-      <c r="F24">
-        <v>39.85</v>
-      </c>
-      <c r="G24">
-        <v>0.02</v>
-      </c>
-      <c r="H24">
-        <v>9961.376002939996</v>
-      </c>
-      <c r="I24">
-        <v>15.19660843580459</v>
-      </c>
-      <c r="J24">
-        <v>-53.8206054958056</v>
-      </c>
-      <c r="K24">
-        <v>-38.62399706000101</v>
-      </c>
-      <c r="L24">
-        <v>13.22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="3">
-        <v>46186.19893202635</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25">
-        <v>0.251223</v>
-      </c>
-      <c r="E25">
-        <v>4242.02</v>
-      </c>
-      <c r="F25">
-        <v>1065.69</v>
-      </c>
-      <c r="G25">
-        <v>0.53</v>
-      </c>
-      <c r="H25">
-        <v>9961.378993399996</v>
-      </c>
-      <c r="I25">
-        <v>15.19959889580446</v>
-      </c>
-      <c r="J25">
-        <v>-53.8206054958056</v>
-      </c>
-      <c r="K25">
-        <v>-38.62100660000115</v>
-      </c>
-      <c r="L25">
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="3">
-        <v>46186.20421433327</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26">
-        <v>0.083158</v>
-      </c>
-      <c r="E26">
-        <v>7427.14</v>
-      </c>
-      <c r="F26">
-        <v>617.63</v>
-      </c>
-      <c r="G26">
-        <v>0.31</v>
-      </c>
-      <c r="H26">
-        <v>9958.181877359995</v>
-      </c>
-      <c r="I26">
-        <v>9.680063660558744</v>
-      </c>
-      <c r="J26">
-        <v>-51.49818630055986</v>
-      </c>
-      <c r="K26">
-        <v>-41.81812264000111</v>
-      </c>
-      <c r="L26">
-        <v>14.06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="3">
-        <v>46186.5862034704</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27">
-        <v>0.109921</v>
-      </c>
-      <c r="E27">
-        <v>7427.14</v>
-      </c>
-      <c r="F27">
-        <v>816.4</v>
-      </c>
-      <c r="G27">
-        <v>0.41</v>
-      </c>
-      <c r="H27">
-        <v>9958.183221419997</v>
-      </c>
-      <c r="I27">
-        <v>6.615357426412629</v>
-      </c>
-      <c r="J27">
-        <v>-48.43213600641379</v>
-      </c>
-      <c r="K27">
-        <v>-41.81677858000116</v>
-      </c>
-      <c r="L27">
-        <v>14.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="3">
-        <v>46186.58621225939</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28">
-        <v>0.084497</v>
-      </c>
-      <c r="E28">
-        <v>4237.78</v>
-      </c>
-      <c r="F28">
-        <v>358.08</v>
-      </c>
-      <c r="G28">
-        <v>0.18</v>
-      </c>
-      <c r="H28">
-        <v>9957.118339239996</v>
-      </c>
-      <c r="I28">
-        <v>5.907433367285421</v>
-      </c>
-      <c r="J28">
-        <v>-48.78909412728657</v>
-      </c>
-      <c r="K28">
-        <v>-42.88166076000115</v>
-      </c>
-      <c r="L28">
-        <v>14.65</v>
+        <v>12.18</v>
       </c>
     </row>
   </sheetData>
@@ -1550,82 +992,82 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>14.65</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>29308.32</v>
+        <v>24320.73</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>-48.79</v>
+        <v>-106.31</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>5.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>-42.88</v>
+        <v>-106.31</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>9957.120000000001</v>
+        <v>9893.690000000001</v>
       </c>
     </row>
   </sheetData>
